--- a/report-010-manual-010.xlsx
+++ b/report-010-manual-010.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>{"baseline_commit": "1adca506cc96d125d6903e311c9cb5ab68401f39", "fix_commit": "f5c53f68c2271567c21f3d9355f83af435a69c07", "fix_passed": true, "red_failed": true, "test_commit": "1d323fcbabd9b6a658709925ae3adb9f7064e8fe"}</t>
+          <t>{"pre_fix": {"commit": "1d323fcbabd9b6a658709925ae3adb9f7064e8fe", "result": "red", "trajectory_url": "未生成"}}</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
